--- a/files/港岛-西营盘及上环-15 Western Street.xlsx
+++ b/files/港岛-西营盘及上环-15 Western Street.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15 Western Street 销控表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -111,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -176,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -192,45 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -702,7 +569,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-28</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -748,7 +615,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-12</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -794,7 +661,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-04-18</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -840,7 +707,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-22</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -886,7 +753,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-12</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -932,7 +799,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -978,7 +845,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1024,7 +891,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1070,7 +937,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-04-07</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1116,7 +983,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-03-09</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1162,7 +1029,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1208,7 +1075,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1254,7 +1121,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1300,7 +1167,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-04-20</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1346,7 +1213,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1392,7 +1259,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-09</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1438,7 +1305,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1484,7 +1351,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1530,7 +1397,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1622,7 +1489,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -1668,7 +1535,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -1714,7 +1581,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-12-11</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -1760,7 +1627,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -1806,7 +1673,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-09</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -1852,7 +1719,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -1898,7 +1765,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -1944,7 +1811,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -1990,7 +1857,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-25</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2036,7 +1903,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2128,7 +1995,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2174,7 +2041,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2220,7 +2087,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-24</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2266,7 +2133,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2312,7 +2179,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-24</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -2358,7 +2225,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -2404,7 +2271,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -2450,7 +2317,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-23</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -2496,7 +2363,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-14</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -2542,7 +2409,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -2588,7 +2455,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -2634,7 +2501,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -2680,7 +2547,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-10-21</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -2726,7 +2593,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -2772,7 +2639,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-23</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -2818,7 +2685,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-06-18</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -2864,7 +2731,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -2910,7 +2777,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-03-09</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -2956,7 +2823,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-22</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3002,7 +2869,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-07-19</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3048,7 +2915,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-02-03</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -3094,7 +2961,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-06-22</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -3140,7 +3007,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-06</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -3186,7 +3053,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -3232,7 +3099,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-07-08</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -3278,7 +3145,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-02-04</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -3324,7 +3191,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-02-03</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -3370,7 +3237,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-02-17</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -3416,7 +3283,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-08</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -3462,7 +3329,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-06-21</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -3508,7 +3375,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-04-15</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -3554,7 +3421,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-02-05</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -3600,7 +3467,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-26</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -3646,7 +3513,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-12</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -3692,7 +3559,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-26</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -3738,7 +3605,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-02-03</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -3784,7 +3651,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-02-03</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -3830,7 +3697,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-30</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -3876,7 +3743,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-07-31</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -3922,7 +3789,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-05-07</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -3968,7 +3835,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-02-04</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -4014,7 +3881,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-28</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -4060,7 +3927,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-29</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -4106,7 +3973,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-08</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -4152,7 +4019,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-02-05</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -4198,7 +4065,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-02-06</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -4244,7 +4111,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-02-04</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -4290,7 +4157,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-04-06</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -4336,7 +4203,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-05</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -4382,7 +4249,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-02-06</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -4428,7 +4295,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-08-02</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -4520,7 +4387,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-04-20</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -4566,7 +4433,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -4612,7 +4479,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-03-08</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -4658,7 +4525,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-04</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -4704,7 +4571,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-02-09</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -4750,7 +4617,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-25</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -4796,7 +4663,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-08</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -4842,7 +4709,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-04-20</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -4888,7 +4755,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-02-04</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -4934,7 +4801,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-17</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -4980,7 +4847,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -5026,7 +4893,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-26</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -5072,7 +4939,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-05-07</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -5118,7 +4985,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-14</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -5164,7 +5031,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -5210,7 +5077,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-03-23</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -5256,7 +5123,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-06-21</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -5302,7 +5169,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-07-14</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -5348,7 +5215,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-10-13</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -5394,7 +5261,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-05-25</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -5440,7 +5307,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-26</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -5486,7 +5353,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-09</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -5508,1156 +5375,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>15 Western Street - 15 Western Street 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>105 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>104 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>31&amp;R/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-$2,588万
-$41,748/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 564呎 (2房)
-$2,272万
-$40,284/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr"/>
-      <c r="E6" s="17" t="inlineStr"/>
-      <c r="F6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-$2,139万
-$34,502/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 530呎 (2房)
-$1,807万
-$34,102/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr"/>
-      <c r="E7" s="17" t="inlineStr"/>
-      <c r="F7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-$2,045万
-$32,987/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 530呎 (2房)
-$1,722万
-$32,485/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr"/>
-      <c r="E8" s="17" t="inlineStr"/>
-      <c r="F8" s="17" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-$1,971万
-$31,787/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 530呎 (2房)
-$1,714万
-$32,345/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr"/>
-      <c r="E9" s="17" t="inlineStr"/>
-      <c r="F9" s="17" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 661呎 (3房)
-$2,414万
-$36,513/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 530呎 (2房)
-$1,610万
-$30,375/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr"/>
-      <c r="E10" s="17" t="inlineStr"/>
-      <c r="F10" s="17" t="inlineStr"/>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 308呎 (1房)
-$1,120万
-$36,364/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 341呎 (1房)
-$1,115万
-$32,695/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>C | 212呎 (开放式)
-$756万
-$35,651/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>D | 212呎 (开放式)
-$756万
-$35,651/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>E | 344呎 (1房)
-$1,141万
-$33,160/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 307呎 (1房)
-$1,297万
-$42,257/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 341呎 (1房)
-$1,097万
-$32,179/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>C | 212呎 (开放式)
-$720万
-$33,953/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>D | 212呎 (开放式)
-$720万
-$33,953/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>E | 344呎 (1房)
-$1,097万
-$31,898/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 307呎 (1房)
-$1,024万
-$33,355/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 341呎 (1房)
-$1,065万
-$31,240/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>C | 212呎 (开放式)
-$703万
-$33,156/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>D | 212呎 (开放式)
-$698万
-$32,934/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>E | 344呎 (1房)
-$1,065万
-$30,968/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 307呎 (1房)
-$1,016万
-$33,091/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 340呎 (1房)
-$1,050万
-$30,871/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>C | 212呎 (开放式)
-$699万
-$32,958/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="inlineStr">
-        <is>
-          <t>D | 212呎 (开放式)
-$699万
-$32,958/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>E | 344呎 (1房)
-$1,050万
-$30,512/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 308呎 (1房)
-$1,008万
-$32,721/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>B | 341呎 (1房)
-$1,044万
-$30,625/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>C | 212呎 (开放式)
-$691万
-$32,575/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>D | 212呎 (开放式)
-$691万
-$32,575/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>E | 344呎 (1房)
-$1,050万
-$30,538/呎
-(21年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 307呎 (1房)
-$1,000万
-$32,567/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>B | 341呎 (1房)
-$1,017万
-$29,830/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>C | 212呎 (开放式)
-$610万
-$28,750/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>D | 212呎 (开放式)
-$687万
-$32,420/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>E | 344呎 (1房)
-$987万
-$28,703/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 308呎 (1房)
-$929万
-$30,173/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 340呎 (1房)
-$992万
-$29,171/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>C | 212呎 (开放式)
-$684万
-$32,269/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="inlineStr">
-        <is>
-          <t>D | 212呎 (开放式)
-$684万
-$32,269/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>E | 344呎 (1房)
-$964万
-$28,017/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 308呎 (1房)
-$982万
-$31,886/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 340呎 (1房)
-$1,025万
-$30,156/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>C | 212呎 (开放式)
-$684万
-$32,259/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>D | 212呎 (开放式)
-$749万
-$35,330/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>E | 344呎 (1房)
-$962万
-$27,959/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>A | 308呎 (1房)
-$920万
-$29,870/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 340呎 (1房)
-$978万
-$28,774/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>C | 213呎 (开放式)
-$656万
-$30,808/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>D | 213呎 (开放式)
-$656万
-$30,808/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>E | 344呎 (1房)
-$996万
-$28,951/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>A | 307呎 (1房)
-$947万
-$30,850/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>B | 341呎 (1房)
-$965万
-$28,296/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>C | 213呎 (开放式)
-$702万
-$32,934/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="inlineStr">
-        <is>
-          <t>D | 212呎 (开放式)
-$702万
-$33,090/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
-        <is>
-          <t>E | 344呎 (1房)
-$971万
-$28,230/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>A | 307呎 (1房)
-$942万
-$30,697/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>B | 340呎 (1房)
-$958万
-$28,182/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>C | 212呎 (开放式)
-$636万
-$30,014/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>D | 213呎 (开放式)
-$667万
-$31,296/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>E | 344呎 (1房)
-$964万
-$28,035/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>A | 308呎 (1房)
-$938万
-$30,445/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>B | 341呎 (1房)
-$997万
-$29,238/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>C | 212呎 (开放式)
-$692万
-$32,651/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E22" s="16" t="inlineStr">
-        <is>
-          <t>D | 212呎 (开放式)
-$692万
-$32,651/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F22" s="16" t="inlineStr">
-        <is>
-          <t>E | 344呎 (1房)
-$925万
-$26,881/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>A | 308呎 (1房)
-$933万
-$30,292/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>B | 341呎 (1房)
-$1,000万
-$29,323/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>C | 213呎 (开放式)
-$658万
-$30,878/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="inlineStr">
-        <is>
-          <t>D | 212呎 (开放式)
-$628万
-$29,613/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F23" s="16" t="inlineStr">
-        <is>
-          <t>E | 344呎 (1房)
-$951万
-$27,648/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>A | 308呎 (1房)
-$908万
-$29,464/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>B | 340呎 (1房)
-$939万
-$27,609/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>C | 213呎 (开放式)
-$683万
-$32,070/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E24" s="16" t="inlineStr">
-        <is>
-          <t>D | 212呎 (开放式)
-$624万
-$29,420/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F24" s="16" t="inlineStr">
-        <is>
-          <t>E | 344呎 (1房)
-$999万
-$29,038/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>A | 307呎 (1房)
-$885万
-$28,827/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>B | 341呎 (1房)
-$1,000万
-$29,323/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="inlineStr">
-        <is>
-          <t>C | 213呎 (开放式)
-$652万
-$30,610/呎
-(20年-01月)</t>
-        </is>
-      </c>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>D | 212呎 (开放式)
-$654万
-$30,844/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F25" s="16" t="inlineStr">
-        <is>
-          <t>E | 344呎 (1房)
-$910万
-$26,459/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>A | 307呎 (1房)
-$870万
-$28,332/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>B | 341呎 (1房)
-$926万
-$27,150/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="inlineStr">
-        <is>
-          <t>C | 212呎 (开放式)
-$615万
-$29,024/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E26" s="16" t="inlineStr">
-        <is>
-          <t>D | 212呎 (开放式)
-$668万
-$31,509/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F26" s="16" t="inlineStr">
-        <is>
-          <t>E | 344呎 (1房)
-$900万
-$26,148/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>A | 308呎 (1房)
-$864万
-$28,045/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>B | 340呎 (1房)
-$980万
-$28,824/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="inlineStr">
-        <is>
-          <t>C | 213呎 (开放式)
-$640万
-$30,061/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E27" s="16" t="inlineStr">
-        <is>
-          <t>D | 212呎 (开放式)
-$633万
-$29,863/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F27" s="16" t="inlineStr">
-        <is>
-          <t>E | 344呎 (1房)
-$978万
-$28,445/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>A | 307呎 (1房)
-$858万
-$27,945/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>B | 341呎 (1房)
-$913万
-$26,777/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D28" s="16" t="inlineStr">
-        <is>
-          <t>C | 212呎 (开放式)
-$636万
-$30,005/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E28" s="16" t="inlineStr">
-        <is>
-          <t>D | 212呎 (开放式)
-$636万
-$30,005/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F28" s="16" t="inlineStr">
-        <is>
-          <t>E | 344呎 (1房)
-$930万
-$27,020/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>A | 307呎 (1房)
-$852万
-$27,752/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>B | 341呎 (1房)
-$907万
-$26,592/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D29" s="16" t="inlineStr">
-        <is>
-          <t>C | 213呎 (开放式)
-$594万
-$27,883/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E29" s="16" t="inlineStr">
-        <is>
-          <t>D | 213呎 (开放式)
-$622万
-$29,211/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F29" s="16" t="inlineStr">
-        <is>
-          <t>E | 344呎 (1房)
-$873万
-$25,387/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/港岛-西营盘及上环-15 Western Street.xlsx
+++ b/files/港岛-西营盘及上环-15 Western Street.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15 Western Street" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +42,90 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +136,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +217,57 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +644,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -5375,4 +5545,1156 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>15 Western Street 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>31&amp;R</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+$2588万
+$41,748/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 564呎 (2房)
+$2272万
+$40,284/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr"/>
+      <c r="F5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+$2139万
+$34,502/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 530呎 (2房)
+$1807万
+$34,102/呎
+(22年-04月)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+$2045万
+$32,987/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 530呎 (2房)
+$1722万
+$32,485/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr"/>
+      <c r="F7" s="21" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+$1971万
+$31,787/呎
+(21年-04月)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 530呎 (2房)
+$1714万
+$32,345/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr"/>
+      <c r="E8" s="21" t="inlineStr"/>
+      <c r="F8" s="21" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 661呎 (3房)
+$2414万
+$36,513/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 530呎 (2房)
+$1610万
+$30,375/呎
+(21年-04月)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr"/>
+      <c r="E9" s="21" t="inlineStr"/>
+      <c r="F9" s="21" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 308呎 (1房)
+$1120万
+$36,364/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 341呎 (1房)
+$1115万
+$32,695/呎
+(22年-04月)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 212呎 (开放式)
+$756万
+$35,651/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 212呎 (开放式)
+$756万
+$35,651/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>E | 344呎 (1房)
+$1141万
+$33,160/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 307呎 (1房)
+$1297万
+$42,257/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 341呎 (1房)
+$1097万
+$32,179/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 212呎 (开放式)
+$720万
+$33,953/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 212呎 (开放式)
+$720万
+$33,953/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>E | 344呎 (1房)
+$1097万
+$31,898/呎
+(21年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 307呎 (1房)
+$1024万
+$33,355/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 341呎 (1房)
+$1065万
+$31,240/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 212呎 (开放式)
+$703万
+$33,156/呎
+(23年-12月)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>D | 212呎 (开放式)
+$698万
+$32,934/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>E | 344呎 (1房)
+$1065万
+$30,968/呎
+(21年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 307呎 (1房)
+$1016万
+$33,091/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 340呎 (1房)
+$1050万
+$30,871/呎
+(21年-08月)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 212呎 (开放式)
+$699万
+$32,958/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>D | 212呎 (开放式)
+$699万
+$32,958/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>E | 344呎 (1房)
+$1050万
+$30,512/呎
+(21年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 308呎 (1房)
+$1008万
+$32,721/呎
+(22年-09月)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 341呎 (1房)
+$1044万
+$30,625/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 212呎 (开放式)
+$691万
+$32,575/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>D | 212呎 (开放式)
+$691万
+$32,575/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>E | 344呎 (1房)
+$1050万
+$30,538/呎
+(21年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 307呎 (1房)
+$1000万
+$32,567/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 341呎 (1房)
+$1017万
+$29,830/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 212呎 (开放式)
+$610万
+$28,750/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 212呎 (开放式)
+$687万
+$32,420/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>E | 344呎 (1房)
+$987万
+$28,703/呎
+(21年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 308呎 (1房)
+$929万
+$30,173/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 340呎 (1房)
+$992万
+$29,171/呎
+(20年-10月)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 212呎 (开放式)
+$684万
+$32,269/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 212呎 (开放式)
+$684万
+$32,269/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>E | 344呎 (1房)
+$964万
+$28,017/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 308呎 (1房)
+$982万
+$31,886/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 340呎 (1房)
+$1025万
+$30,156/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 212呎 (开放式)
+$684万
+$32,259/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>D | 212呎 (开放式)
+$749万
+$35,330/呎
+(20年-06月)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>E | 344呎 (1房)
+$962万
+$27,959/呎
+(21年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 308呎 (1房)
+$920万
+$29,870/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 340呎 (1房)
+$978万
+$28,774/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 213呎 (开放式)
+$656万
+$30,808/呎
+(20年-06月)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>D | 213呎 (开放式)
+$656万
+$30,808/呎
+(20年-02月)</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>E | 344呎 (1房)
+$996万
+$28,951/呎
+(20年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 307呎 (1房)
+$947万
+$30,850/呎
+(21年-08月)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 341呎 (1房)
+$965万
+$28,296/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 213呎 (开放式)
+$702万
+$32,934/呎
+(20年-02月)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>D | 212呎 (开放式)
+$702万
+$33,090/呎
+(20年-02月)</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>E | 344呎 (1房)
+$971万
+$28,230/呎
+(20年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 307呎 (1房)
+$942万
+$30,697/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 340呎 (1房)
+$958万
+$28,182/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 212呎 (开放式)
+$636万
+$30,014/呎
+(20年-02月)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>D | 213呎 (开放式)
+$667万
+$31,296/呎
+(20年-04月)</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>E | 344呎 (1房)
+$964万
+$28,035/呎
+(20年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 308呎 (1房)
+$938万
+$30,445/呎
+(22年-07月)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 341呎 (1房)
+$997万
+$29,238/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 212呎 (开放式)
+$692万
+$32,651/呎
+(20年-02月)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>D | 212呎 (开放式)
+$692万
+$32,651/呎
+(20年-02月)</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>E | 344呎 (1房)
+$925万
+$26,881/呎
+(21年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 308呎 (1房)
+$933万
+$30,292/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 341呎 (1房)
+$1000万
+$29,323/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 213呎 (开放式)
+$658万
+$30,878/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>D | 212呎 (开放式)
+$628万
+$29,613/呎
+(20年-02月)</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>E | 344呎 (1房)
+$951万
+$27,648/呎
+(20年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 308呎 (1房)
+$908万
+$29,464/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 340呎 (1房)
+$939万
+$27,609/呎
+(21年-04月)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 213呎 (开放式)
+$683万
+$32,070/呎
+(20年-02月)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>D | 212呎 (开放式)
+$624万
+$29,420/呎
+(20年-02月)</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>E | 344呎 (1房)
+$999万
+$29,038/呎
+(20年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 307呎 (1房)
+$885万
+$28,827/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 341呎 (1房)
+$1000万
+$29,323/呎
+(22年-04月)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 213呎 (开放式)
+$652万
+$30,610/呎
+(20年-01月)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>D | 212呎 (开放式)
+$654万
+$30,844/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>E | 344呎 (1房)
+$910万
+$26,459/呎
+(20年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 307呎 (1房)
+$870万
+$28,332/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>B | 341呎 (1房)
+$926万
+$27,150/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>C | 212呎 (开放式)
+$615万
+$29,024/呎
+(20年-02月)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>D | 212呎 (开放式)
+$668万
+$31,509/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>E | 344呎 (1房)
+$900万
+$26,148/呎
+(21年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>A | 308呎 (1房)
+$864万
+$28,045/呎
+(21年-08月)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>B | 340呎 (1房)
+$980万
+$28,824/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>C | 213呎 (开放式)
+$640万
+$30,061/呎
+(21年-08月)</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>D | 212呎 (开放式)
+$633万
+$29,863/呎
+(20年-02月)</t>
+        </is>
+      </c>
+      <c r="F26" s="20" t="inlineStr">
+        <is>
+          <t>E | 344呎 (1房)
+$978万
+$28,445/呎
+(20年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>A | 307呎 (1房)
+$858万
+$27,945/呎
+(20年-06月)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>B | 341呎 (1房)
+$913万
+$26,777/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>C | 212呎 (开放式)
+$636万
+$30,005/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>D | 212呎 (开放式)
+$636万
+$30,005/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>E | 344呎 (1房)
+$930万
+$27,020/呎
+(20年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 307呎 (1房)
+$852万
+$27,752/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>B | 341呎 (1房)
+$907万
+$26,592/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>C | 213呎 (开放式)
+$594万
+$27,883/呎
+(20年-05月)</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>D | 213呎 (开放式)
+$622万
+$29,211/呎
+(20年-10月)</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="inlineStr">
+        <is>
+          <t>E | 344呎 (1房)
+$873万
+$25,387/呎
+(20年-07月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/港岛-西营盘及上环-15 Western Street.xlsx
+++ b/files/港岛-西营盘及上环-15 Western Street.xlsx
@@ -644,7 +644,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-西营盘及上环-15 Western Street.xlsx
+++ b/files/港岛-西营盘及上环-15 Western Street.xlsx
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J107"/>
+  <dimension ref="A1:N107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -647,6 +647,10 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -704,6 +708,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -750,6 +774,22 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>22720000</v>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>40284</v>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -796,6 +836,22 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>25884000</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>41748</v>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -842,6 +898,22 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>18074000</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>34102</v>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -888,6 +960,22 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>21391000</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>34502</v>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -934,6 +1022,22 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>17217000</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>32485</v>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -980,6 +1084,22 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>20452000</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>32987</v>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1026,6 +1146,22 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>17143000</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>32345</v>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1072,6 +1208,22 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>19708000</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>31787</v>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1118,6 +1270,22 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>16099000</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>30375</v>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1164,6 +1332,22 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>24135000</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>36513</v>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1210,6 +1394,22 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>11407000</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>33160</v>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1256,6 +1456,22 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>7558000</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>35651</v>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1302,6 +1518,22 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>7558000</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>35651</v>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1348,6 +1580,22 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>11149000</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>32695</v>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1394,6 +1642,22 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>11200000</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>36364</v>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1440,6 +1704,22 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>10973000</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>31898</v>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1486,6 +1766,22 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>7198000</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>33953</v>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1532,6 +1828,22 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>7198000</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>33953</v>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1578,6 +1890,22 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>10973000</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>32179</v>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1624,6 +1952,22 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>26%</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>9664885</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>31482</v>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>120天即供優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1670,6 +2014,22 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>10653000</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>30968</v>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1716,6 +2076,22 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>6982000</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>32934</v>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1762,6 +2138,22 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>7029000</v>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>33156</v>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1808,6 +2200,22 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>10653000</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>31240</v>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1854,6 +2262,22 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>10240000</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>33355</v>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1900,6 +2324,22 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>10496000</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>30512</v>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1946,6 +2386,22 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>6987000</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>32958</v>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1992,6 +2448,22 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>6987000</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>32958</v>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2038,6 +2510,22 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>10496000</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>30871</v>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2084,6 +2572,22 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>10159000</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>33091</v>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2130,6 +2634,22 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>10505000</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>30538</v>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2176,6 +2696,22 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>6906000</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>32575</v>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2222,6 +2758,22 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>6906000</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>32575</v>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2268,6 +2820,22 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>10443000</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>30625</v>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2314,6 +2882,22 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>10078000</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>32721</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2360,6 +2944,22 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>9874000</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>28703</v>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2406,6 +3006,22 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>6873000</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>32420</v>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2452,6 +3068,22 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>6095000</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>28750</v>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2498,6 +3130,22 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>10172000</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>29830</v>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2544,6 +3192,22 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>9998000</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>32567</v>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2590,6 +3254,22 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>9638000</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>28017</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2636,6 +3316,22 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>6841000</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>32269</v>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2682,6 +3378,22 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>6841000</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>32269</v>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2728,6 +3440,22 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>9918000</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>29171</v>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2774,6 +3502,22 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>9293400</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>30173</v>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2820,6 +3564,22 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>9618000</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>27959</v>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2866,6 +3626,22 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>7490000</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>35330</v>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2912,6 +3688,22 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>6839000</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>32259</v>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2958,6 +3750,22 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>10253000</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>30156</v>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3004,6 +3812,22 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>9821000</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>31886</v>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3050,6 +3874,22 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>9959000</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>28951</v>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3096,6 +3936,22 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>6562000</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>30808</v>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3142,6 +3998,22 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>6562000</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>30808</v>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3188,6 +4060,22 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>9783000</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>28774</v>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3234,6 +4122,22 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>9200000</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>29870</v>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3280,6 +4184,22 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>9711000</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>28230</v>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3326,6 +4246,22 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>7015000</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>33090</v>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3372,6 +4308,22 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>7015000</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>32934</v>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3418,6 +4370,22 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="n">
+        <v>9649000</v>
+      </c>
+      <c r="L61" s="5" t="n">
+        <v>28296</v>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3464,6 +4432,22 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>9471000</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>30850</v>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3510,6 +4494,22 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="n">
+        <v>9644000</v>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v>28035</v>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3556,6 +4556,22 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>6666000</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>31296</v>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3602,6 +4618,22 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="n">
+        <v>6363000</v>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v>30014</v>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3648,6 +4680,22 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>9582000</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>28182</v>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3694,6 +4742,22 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="n">
+        <v>9424000</v>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>30697</v>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3740,6 +4804,22 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="n">
+        <v>9247000</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>26881</v>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3786,6 +4866,22 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>6922000</v>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>32651</v>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3832,6 +4928,22 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="n">
+        <v>6922000</v>
+      </c>
+      <c r="L70" s="5" t="n">
+        <v>32651</v>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3878,6 +4990,22 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="n">
+        <v>9970000</v>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v>29238</v>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3924,6 +5052,22 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>9377000</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>30445</v>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3970,6 +5114,22 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>9511000</v>
+      </c>
+      <c r="L73" s="5" t="n">
+        <v>27648</v>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4016,6 +5176,22 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>6278000</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>29613</v>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4062,6 +5238,22 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v>6577000</v>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>30878</v>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4108,6 +5300,22 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="n">
+        <v>9999000</v>
+      </c>
+      <c r="L76" s="5" t="n">
+        <v>29323</v>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4154,6 +5362,22 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="n">
+        <v>9330000</v>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>30292</v>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4200,6 +5424,22 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="n">
+        <v>9989000</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>29038</v>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4246,6 +5486,22 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="n">
+        <v>6237000</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>29420</v>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4292,6 +5548,22 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="n">
+        <v>6831000</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>32070</v>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4338,6 +5610,22 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="n">
+        <v>9387000</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>27609</v>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4384,6 +5672,22 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="n">
+        <v>9075000</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>29464</v>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4430,6 +5734,22 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>9102000</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>26459</v>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4476,6 +5796,22 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>6539000</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>30844</v>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4522,6 +5858,22 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>6520000</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>30610</v>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4568,6 +5920,22 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="5" t="n">
+        <v>9999000</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>29323</v>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4614,6 +5982,22 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>8850000</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>28827</v>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4660,6 +6044,22 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>8995000</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>26148</v>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4706,6 +6106,22 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>6680000</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>31509</v>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4752,6 +6168,22 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>6153000</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>29024</v>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4798,6 +6230,22 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="5" t="n">
+        <v>9258000</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>27150</v>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4844,6 +6292,22 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K92" s="5" t="n">
+        <v>8698000</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>28332</v>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4890,6 +6354,22 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>9785000</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>28445</v>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4936,6 +6416,22 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>6331000</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>29863</v>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4982,6 +6478,22 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="5" t="n">
+        <v>6403000</v>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v>30061</v>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5028,6 +6540,22 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="5" t="n">
+        <v>9800000</v>
+      </c>
+      <c r="L96" s="5" t="n">
+        <v>28824</v>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5074,6 +6602,22 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="5" t="n">
+        <v>8638000</v>
+      </c>
+      <c r="L97" s="5" t="n">
+        <v>28045</v>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5120,6 +6664,22 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="5" t="n">
+        <v>9295000</v>
+      </c>
+      <c r="L98" s="5" t="n">
+        <v>27020</v>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5166,6 +6726,22 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v>6361000</v>
+      </c>
+      <c r="L99" s="5" t="n">
+        <v>30005</v>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5212,6 +6788,22 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K100" s="5" t="n">
+        <v>6361000</v>
+      </c>
+      <c r="L100" s="5" t="n">
+        <v>30005</v>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5258,6 +6850,22 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="5" t="n">
+        <v>9131000</v>
+      </c>
+      <c r="L101" s="5" t="n">
+        <v>26777</v>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5304,6 +6912,22 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="5" t="n">
+        <v>8579000</v>
+      </c>
+      <c r="L102" s="5" t="n">
+        <v>27945</v>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5350,6 +6974,22 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="5" t="n">
+        <v>8733000</v>
+      </c>
+      <c r="L103" s="5" t="n">
+        <v>25387</v>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5396,6 +7036,22 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K104" s="5" t="n">
+        <v>6222000</v>
+      </c>
+      <c r="L104" s="5" t="n">
+        <v>29211</v>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N104" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5442,6 +7098,22 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="5" t="n">
+        <v>5939000</v>
+      </c>
+      <c r="L105" s="5" t="n">
+        <v>27883</v>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5488,6 +7160,22 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K106" s="5" t="n">
+        <v>9068000</v>
+      </c>
+      <c r="L106" s="5" t="n">
+        <v>26592</v>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5534,13 +7222,29 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="5" t="n">
+        <v>8520000</v>
+      </c>
+      <c r="L107" s="5" t="n">
+        <v>27752</v>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N107" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -5678,7 +7382,7 @@
           <t>A | 620呎 (3房)
 $2588万
 $41,748/呎
-(21年-07月)</t>
+(21年-07月-12日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -5686,7 +7390,7 @@
           <t>B | 564呎 (2房)
 $2272万
 $40,284/呎
-(21年-06月)</t>
+(21年-06月-28日)</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr"/>
@@ -5704,7 +7408,7 @@
           <t>A | 620呎 (3房)
 $2139万
 $34,502/呎
-(22年-02月)</t>
+(22年-02月-22日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -5712,7 +7416,7 @@
           <t>B | 530呎 (2房)
 $1807万
 $34,102/呎
-(22年-04月)</t>
+(22年-04月-18日)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr"/>
@@ -5730,7 +7434,7 @@
           <t>A | 620呎 (3房)
 $2045万
 $32,987/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -5738,7 +7442,7 @@
           <t>B | 530呎 (2房)
 $1722万
 $32,485/呎
-(21年-12月)</t>
+(21年-12月-12日)</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr"/>
@@ -5756,7 +7460,7 @@
           <t>A | 620呎 (3房)
 $1971万
 $31,787/呎
-(21年-04月)</t>
+(21年-04月-07日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -5764,7 +7468,7 @@
           <t>B | 530呎 (2房)
 $1714万
 $32,345/呎
-(21年-11月)</t>
+(21年-11月-30日)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr"/>
@@ -5782,7 +7486,7 @@
           <t>A | 661呎 (3房)
 $2414万
 $36,513/呎
-(21年-03月)</t>
+(21年-03月-09日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -5790,7 +7494,7 @@
           <t>B | 530呎 (2房)
 $1610万
 $30,375/呎
-(21年-04月)</t>
+(21年-04月-07日)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr"/>
@@ -5808,7 +7512,7 @@
           <t>A | 308呎 (1房)
 $1120万
 $36,364/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -5816,7 +7520,7 @@
           <t>B | 341呎 (1房)
 $1115万
 $32,695/呎
-(22年-04月)</t>
+(22年-04月-20日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -5824,7 +7528,7 @@
           <t>C | 212呎 (开放式)
 $756万
 $35,651/呎
-(24年-03月)</t>
+(24年-03月-26日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -5832,7 +7536,7 @@
           <t>D | 212呎 (开放式)
 $756万
 $35,651/呎
-(24年-03月)</t>
+(24年-03月-26日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -5840,7 +7544,7 @@
           <t>E | 344呎 (1房)
 $1141万
 $33,160/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
     </row>
@@ -5863,7 +7567,7 @@
           <t>B | 341呎 (1房)
 $1097万
 $32,179/呎
-(21年-06月)</t>
+(21年-06月-24日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -5871,7 +7575,7 @@
           <t>C | 212呎 (开放式)
 $720万
 $33,953/呎
-(24年-03月)</t>
+(24年-03月-26日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -5879,7 +7583,7 @@
           <t>D | 212呎 (开放式)
 $720万
 $33,953/呎
-(24年-03月)</t>
+(24年-03月-26日)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -5887,7 +7591,7 @@
           <t>E | 344呎 (1房)
 $1097万
 $31,898/呎
-(21年-12月)</t>
+(21年-12月-09日)</t>
         </is>
       </c>
     </row>
@@ -5902,7 +7606,7 @@
           <t>A | 307呎 (1房)
 $1024万
 $33,355/呎
-(21年-12月)</t>
+(21年-12月-09日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -5910,7 +7614,7 @@
           <t>B | 341呎 (1房)
 $1065万
 $31,240/呎
-(21年-09月)</t>
+(21年-09月-23日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -5918,7 +7622,7 @@
           <t>C | 212呎 (开放式)
 $703万
 $33,156/呎
-(23年-12月)</t>
+(23年-12月-11日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -5926,7 +7630,7 @@
           <t>D | 212呎 (开放式)
 $698万
 $32,934/呎
-(24年-04月)</t>
+(24年-04月-10日)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -5934,7 +7638,7 @@
           <t>E | 344呎 (1房)
 $1065万
 $30,968/呎
-(21年-06月)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
     </row>
@@ -5949,7 +7653,7 @@
           <t>A | 307呎 (1房)
 $1016万
 $33,091/呎
-(21年-09月)</t>
+(21年-09月-09日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -5957,7 +7661,7 @@
           <t>B | 340呎 (1房)
 $1050万
 $30,871/呎
-(21年-08月)</t>
+(21年-08月-25日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -5965,7 +7669,7 @@
           <t>C | 212呎 (开放式)
 $699万
 $32,958/呎
-(24年-03月)</t>
+(24年-03月-17日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -5973,7 +7677,7 @@
           <t>D | 212呎 (开放式)
 $699万
 $32,958/呎
-(24年-03月)</t>
+(24年-03月-17日)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -5981,7 +7685,7 @@
           <t>E | 344呎 (1房)
 $1050万
 $30,512/呎
-(21年-11月)</t>
+(21年-11月-30日)</t>
         </is>
       </c>
     </row>
@@ -5996,7 +7700,7 @@
           <t>A | 308呎 (1房)
 $1008万
 $32,721/呎
-(22年-09月)</t>
+(22年-09月-26日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -6004,7 +7708,7 @@
           <t>B | 341呎 (1房)
 $1044万
 $30,625/呎
-(21年-05月)</t>
+(21年-05月-24日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -6012,7 +7716,7 @@
           <t>C | 212呎 (开放式)
 $691万
 $32,575/呎
-(24年-03月)</t>
+(24年-03月-17日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -6020,7 +7724,7 @@
           <t>D | 212呎 (开放式)
 $691万
 $32,575/呎
-(24年-03月)</t>
+(24年-03月-17日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -6028,7 +7732,7 @@
           <t>E | 344呎 (1房)
 $1050万
 $30,538/呎
-(21年-05月)</t>
+(21年-05月-01日)</t>
         </is>
       </c>
     </row>
@@ -6043,7 +7747,7 @@
           <t>A | 307呎 (1房)
 $1000万
 $32,567/呎
-(21年-10月)</t>
+(21年-10月-14日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -6051,7 +7755,7 @@
           <t>B | 341呎 (1房)
 $1017万
 $29,830/呎
-(21年-05月)</t>
+(21年-05月-23日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -6059,7 +7763,7 @@
           <t>C | 212呎 (开放式)
 $610万
 $28,750/呎
-(26年-01月)</t>
+(26年-01月-07日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -6067,7 +7771,7 @@
           <t>D | 212呎 (开放式)
 $687万
 $32,420/呎
-(24年-03月)</t>
+(24年-03月-17日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -6075,7 +7779,7 @@
           <t>E | 344呎 (1房)
 $987万
 $28,703/呎
-(21年-05月)</t>
+(21年-05月-24日)</t>
         </is>
       </c>
     </row>
@@ -6090,7 +7794,7 @@
           <t>A | 308呎 (1房)
 $929万
 $30,173/呎
-(25年-05月)</t>
+(25年-05月-28日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -6098,7 +7802,7 @@
           <t>B | 340呎 (1房)
 $992万
 $29,171/呎
-(20年-10月)</t>
+(20年-10月-21日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -6106,7 +7810,7 @@
           <t>C | 212呎 (开放式)
 $684万
 $32,269/呎
-(22年-08月)</t>
+(22年-08月-01日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -6114,7 +7818,7 @@
           <t>D | 212呎 (开放式)
 $684万
 $32,269/呎
-(24年-03月)</t>
+(24年-03月-17日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -6122,7 +7826,7 @@
           <t>E | 344呎 (1房)
 $964万
 $28,017/呎
-(21年-02月)</t>
+(21年-02月-25日)</t>
         </is>
       </c>
     </row>
@@ -6137,7 +7841,7 @@
           <t>A | 308呎 (1房)
 $982万
 $31,886/呎
-(21年-12月)</t>
+(21年-12月-22日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -6145,7 +7849,7 @@
           <t>B | 340呎 (1房)
 $1025万
 $30,156/呎
-(21年-03月)</t>
+(21年-03月-09日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -6153,7 +7857,7 @@
           <t>C | 212呎 (开放式)
 $684万
 $32,259/呎
-(23年-10月)</t>
+(23年-10月-04日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -6161,7 +7865,7 @@
           <t>D | 212呎 (开放式)
 $749万
 $35,330/呎
-(20年-06月)</t>
+(20年-06月-18日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -6169,7 +7873,7 @@
           <t>E | 344呎 (1房)
 $962万
 $27,959/呎
-(21年-05月)</t>
+(21年-05月-23日)</t>
         </is>
       </c>
     </row>
@@ -6184,7 +7888,7 @@
           <t>A | 308呎 (1房)
 $920万
 $29,870/呎
-(25年-09月)</t>
+(25年-09月-21日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -6192,7 +7896,7 @@
           <t>B | 340呎 (1房)
 $978万
 $28,774/呎
-(21年-06月)</t>
+(21年-06月-06日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -6200,7 +7904,7 @@
           <t>C | 213呎 (开放式)
 $656万
 $30,808/呎
-(20年-06月)</t>
+(20年-06月-22日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -6208,7 +7912,7 @@
           <t>D | 213呎 (开放式)
 $656万
 $30,808/呎
-(20年-02月)</t>
+(20年-02月-03日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -6216,7 +7920,7 @@
           <t>E | 344呎 (1房)
 $996万
 $28,951/呎
-(20年-07月)</t>
+(20年-07月-19日)</t>
         </is>
       </c>
     </row>
@@ -6231,7 +7935,7 @@
           <t>A | 307呎 (1房)
 $947万
 $30,850/呎
-(21年-08月)</t>
+(21年-08月-08日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -6239,7 +7943,7 @@
           <t>B | 341呎 (1房)
 $965万
 $28,296/呎
-(21年-02月)</t>
+(21年-02月-17日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -6247,7 +7951,7 @@
           <t>C | 213呎 (开放式)
 $702万
 $32,934/呎
-(20年-02月)</t>
+(20年-02月-03日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -6255,7 +7959,7 @@
           <t>D | 212呎 (开放式)
 $702万
 $33,090/呎
-(20年-02月)</t>
+(20年-02月-04日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -6263,7 +7967,7 @@
           <t>E | 344呎 (1房)
 $971万
 $28,230/呎
-(20年-07月)</t>
+(20年-07月-08日)</t>
         </is>
       </c>
     </row>
@@ -6278,7 +7982,7 @@
           <t>A | 307呎 (1房)
 $942万
 $30,697/呎
-(21年-09月)</t>
+(21年-09月-12日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -6286,7 +7990,7 @@
           <t>B | 340呎 (1房)
 $958万
 $28,182/呎
-(21年-05月)</t>
+(21年-05月-26日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -6294,7 +7998,7 @@
           <t>C | 212呎 (开放式)
 $636万
 $30,014/呎
-(20年-02月)</t>
+(20年-02月-05日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -6302,7 +8006,7 @@
           <t>D | 213呎 (开放式)
 $667万
 $31,296/呎
-(20年-04月)</t>
+(20年-04月-15日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -6310,7 +8014,7 @@
           <t>E | 344呎 (1房)
 $964万
 $28,035/呎
-(20年-06月)</t>
+(20年-06月-21日)</t>
         </is>
       </c>
     </row>
@@ -6325,7 +8029,7 @@
           <t>A | 308呎 (1房)
 $938万
 $30,445/呎
-(22年-07月)</t>
+(22年-07月-31日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -6333,7 +8037,7 @@
           <t>B | 341呎 (1房)
 $997万
 $29,238/呎
-(20年-12月)</t>
+(20年-12月-30日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -6341,7 +8045,7 @@
           <t>C | 212呎 (开放式)
 $692万
 $32,651/呎
-(20年-02月)</t>
+(20年-02月-03日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -6349,7 +8053,7 @@
           <t>D | 212呎 (开放式)
 $692万
 $32,651/呎
-(20年-02月)</t>
+(20年-02月-03日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -6357,7 +8061,7 @@
           <t>E | 344呎 (1房)
 $925万
 $26,881/呎
-(21年-05月)</t>
+(21年-05月-26日)</t>
         </is>
       </c>
     </row>
@@ -6372,7 +8076,7 @@
           <t>A | 308呎 (1房)
 $933万
 $30,292/呎
-(21年-12月)</t>
+(21年-12月-08日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -6380,7 +8084,7 @@
           <t>B | 341呎 (1房)
 $1000万
 $29,323/呎
-(21年-09月)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -6388,7 +8092,7 @@
           <t>C | 213呎 (开放式)
 $658万
 $30,878/呎
-(21年-06月)</t>
+(21年-06月-28日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -6396,7 +8100,7 @@
           <t>D | 212呎 (开放式)
 $628万
 $29,613/呎
-(20年-02月)</t>
+(20年-02月-04日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -6404,7 +8108,7 @@
           <t>E | 344呎 (1房)
 $951万
 $27,648/呎
-(20年-05月)</t>
+(20年-05月-07日)</t>
         </is>
       </c>
     </row>
@@ -6419,7 +8123,7 @@
           <t>A | 308呎 (1房)
 $908万
 $29,464/呎
-(21年-07月)</t>
+(21年-07月-05日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -6427,7 +8131,7 @@
           <t>B | 340呎 (1房)
 $939万
 $27,609/呎
-(21年-04月)</t>
+(21年-04月-06日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -6435,7 +8139,7 @@
           <t>C | 213呎 (开放式)
 $683万
 $32,070/呎
-(20年-02月)</t>
+(20年-02月-04日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -6443,7 +8147,7 @@
           <t>D | 212呎 (开放式)
 $624万
 $29,420/呎
-(20年-02月)</t>
+(20年-02月-06日)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -6451,7 +8155,7 @@
           <t>E | 344呎 (1房)
 $999万
 $29,038/呎
-(20年-02月)</t>
+(20年-02月-05日)</t>
         </is>
       </c>
     </row>
@@ -6466,7 +8170,7 @@
           <t>A | 307呎 (1房)
 $885万
 $28,827/呎
-(21年-06月)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -6474,7 +8178,7 @@
           <t>B | 341呎 (1房)
 $1000万
 $29,323/呎
-(22年-04月)</t>
+(22年-04月-20日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -6482,7 +8186,7 @@
           <t>C | 213呎 (开放式)
 $652万
 $30,610/呎
-(20年-01月)</t>
+(20年-01月-09日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -6490,7 +8194,7 @@
           <t>D | 212呎 (开放式)
 $654万
 $30,844/呎
-(23年-08月)</t>
+(23年-08月-02日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -6498,7 +8202,7 @@
           <t>E | 344呎 (1房)
 $910万
 $26,459/呎
-(20年-02月)</t>
+(20年-02月-06日)</t>
         </is>
       </c>
     </row>
@@ -6513,7 +8217,7 @@
           <t>A | 307呎 (1房)
 $870万
 $28,332/呎
-(21年-07月)</t>
+(21年-07月-08日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -6521,7 +8225,7 @@
           <t>B | 341呎 (1房)
 $926万
 $27,150/呎
-(21年-05月)</t>
+(21年-05月-25日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -6529,7 +8233,7 @@
           <t>C | 212呎 (开放式)
 $615万
 $29,024/呎
-(20年-02月)</t>
+(20年-02月-09日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -6537,7 +8241,7 @@
           <t>D | 212呎 (开放式)
 $668万
 $31,509/呎
-(22年-05月)</t>
+(22年-05月-04日)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -6545,7 +8249,7 @@
           <t>E | 344呎 (1房)
 $900万
 $26,148/呎
-(21年-03月)</t>
+(21年-03月-08日)</t>
         </is>
       </c>
     </row>
@@ -6560,7 +8264,7 @@
           <t>A | 308呎 (1房)
 $864万
 $28,045/呎
-(21年-08月)</t>
+(21年-08月-26日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -6568,7 +8272,7 @@
           <t>B | 340呎 (1房)
 $980万
 $28,824/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -6576,7 +8280,7 @@
           <t>C | 213呎 (开放式)
 $640万
 $30,061/呎
-(21年-08月)</t>
+(21年-08月-17日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -6584,7 +8288,7 @@
           <t>D | 212呎 (开放式)
 $633万
 $29,863/呎
-(20年-02月)</t>
+(20年-02月-04日)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -6592,7 +8296,7 @@
           <t>E | 344呎 (1房)
 $978万
 $28,445/呎
-(20年-04月)</t>
+(20年-04月-20日)</t>
         </is>
       </c>
     </row>
@@ -6607,7 +8311,7 @@
           <t>A | 307呎 (1房)
 $858万
 $27,945/呎
-(20年-06月)</t>
+(20年-06月-21日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -6615,7 +8319,7 @@
           <t>B | 341呎 (1房)
 $913万
 $26,777/呎
-(21年-03月)</t>
+(21年-03月-23日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -6623,7 +8327,7 @@
           <t>C | 212呎 (开放式)
 $636万
 $30,005/呎
-(21年-09月)</t>
+(21年-09月-01日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -6631,7 +8335,7 @@
           <t>D | 212呎 (开放式)
 $636万
 $30,005/呎
-(21年-06月)</t>
+(21年-06月-14日)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -6639,7 +8343,7 @@
           <t>E | 344呎 (1房)
 $930万
 $27,020/呎
-(20年-05月)</t>
+(20年-05月-07日)</t>
         </is>
       </c>
     </row>
@@ -6654,7 +8358,7 @@
           <t>A | 307呎 (1房)
 $852万
 $27,752/呎
-(21年-11月)</t>
+(21年-11月-09日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -6662,7 +8366,7 @@
           <t>B | 341呎 (1房)
 $907万
 $26,592/呎
-(21年-05月)</t>
+(21年-05月-26日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -6670,7 +8374,7 @@
           <t>C | 213呎 (开放式)
 $594万
 $27,883/呎
-(20年-05月)</t>
+(20年-05月-25日)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -6678,7 +8382,7 @@
           <t>D | 213呎 (开放式)
 $622万
 $29,211/呎
-(20年-10月)</t>
+(20年-10月-13日)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -6686,7 +8390,7 @@
           <t>E | 344呎 (1房)
 $873万
 $25,387/呎
-(20年-07月)</t>
+(20年-07月-14日)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-西营盘及上环-15 Western Street.xlsx
+++ b/files/港岛-西营盘及上环-15 Western Street.xlsx
@@ -1952,14 +1952,14 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>17%</t>
         </is>
       </c>
       <c r="K22" s="5" t="n">
-        <v>9664885</v>
+        <v>10767590</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>31482</v>
+        <v>35074</v>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>

--- a/files/港岛-西营盘及上环-15 Western Street.xlsx
+++ b/files/港岛-西营盘及上环-15 Western Street.xlsx
@@ -7382,7 +7382,7 @@
           <t>A | 620呎 (3房)
 $2588万
 $41,748/呎
-(21年-07月-12日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -7390,7 +7390,7 @@
           <t>B | 564呎 (2房)
 $2272万
 $40,284/呎
-(21年-06月-28日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr"/>
@@ -7408,7 +7408,7 @@
           <t>A | 620呎 (3房)
 $2139万
 $34,502/呎
-(22年-02月-22日)</t>
+(22年-02月)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -7416,7 +7416,7 @@
           <t>B | 530呎 (2房)
 $1807万
 $34,102/呎
-(22年-04月-18日)</t>
+(22年-04月)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr"/>
@@ -7434,7 +7434,7 @@
           <t>A | 620呎 (3房)
 $2045万
 $32,987/呎
-(21年-06月-01日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -7442,7 +7442,7 @@
           <t>B | 530呎 (2房)
 $1722万
 $32,485/呎
-(21年-12月-12日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr"/>
@@ -7460,7 +7460,7 @@
           <t>A | 620呎 (3房)
 $1971万
 $31,787/呎
-(21年-04月-07日)</t>
+(21年-04月)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -7468,7 +7468,7 @@
           <t>B | 530呎 (2房)
 $1714万
 $32,345/呎
-(21年-11月-30日)</t>
+(21年-11月)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr"/>
@@ -7486,7 +7486,7 @@
           <t>A | 661呎 (3房)
 $2414万
 $36,513/呎
-(21年-03月-09日)</t>
+(21年-03月)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -7494,7 +7494,7 @@
           <t>B | 530呎 (2房)
 $1610万
 $30,375/呎
-(21年-04月-07日)</t>
+(21年-04月)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr"/>
@@ -7512,7 +7512,7 @@
           <t>A | 308呎 (1房)
 $1120万
 $36,364/呎
-(26年-05月-03日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -7520,7 +7520,7 @@
           <t>B | 341呎 (1房)
 $1115万
 $32,695/呎
-(22年-04月-20日)</t>
+(22年-04月)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -7528,7 +7528,7 @@
           <t>C | 212呎 (开放式)
 $756万
 $35,651/呎
-(24年-03月-26日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -7536,7 +7536,7 @@
           <t>D | 212呎 (开放式)
 $756万
 $35,651/呎
-(24年-03月-26日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -7544,7 +7544,7 @@
           <t>E | 344呎 (1房)
 $1141万
 $33,160/呎
-(26年-05月-03日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
           <t>B | 341呎 (1房)
 $1097万
 $32,179/呎
-(21年-06月-24日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -7575,7 +7575,7 @@
           <t>C | 212呎 (开放式)
 $720万
 $33,953/呎
-(24年-03月-26日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -7583,7 +7583,7 @@
           <t>D | 212呎 (开放式)
 $720万
 $33,953/呎
-(24年-03月-26日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -7591,7 +7591,7 @@
           <t>E | 344呎 (1房)
 $1097万
 $31,898/呎
-(21年-12月-09日)</t>
+(21年-12月)</t>
         </is>
       </c>
     </row>
@@ -7606,7 +7606,7 @@
           <t>A | 307呎 (1房)
 $1024万
 $33,355/呎
-(21年-12月-09日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -7614,7 +7614,7 @@
           <t>B | 341呎 (1房)
 $1065万
 $31,240/呎
-(21年-09月-23日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -7622,7 +7622,7 @@
           <t>C | 212呎 (开放式)
 $703万
 $33,156/呎
-(23年-12月-11日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -7630,7 +7630,7 @@
           <t>D | 212呎 (开放式)
 $698万
 $32,934/呎
-(24年-04月-10日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -7638,7 +7638,7 @@
           <t>E | 344呎 (1房)
 $1065万
 $30,968/呎
-(21年-06月-02日)</t>
+(21年-06月)</t>
         </is>
       </c>
     </row>
@@ -7653,7 +7653,7 @@
           <t>A | 307呎 (1房)
 $1016万
 $33,091/呎
-(21年-09月-09日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -7661,7 +7661,7 @@
           <t>B | 340呎 (1房)
 $1050万
 $30,871/呎
-(21年-08月-25日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -7669,7 +7669,7 @@
           <t>C | 212呎 (开放式)
 $699万
 $32,958/呎
-(24年-03月-17日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -7677,7 +7677,7 @@
           <t>D | 212呎 (开放式)
 $699万
 $32,958/呎
-(24年-03月-17日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -7685,7 +7685,7 @@
           <t>E | 344呎 (1房)
 $1050万
 $30,512/呎
-(21年-11月-30日)</t>
+(21年-11月)</t>
         </is>
       </c>
     </row>
@@ -7700,7 +7700,7 @@
           <t>A | 308呎 (1房)
 $1008万
 $32,721/呎
-(22年-09月-26日)</t>
+(22年-09月)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -7708,7 +7708,7 @@
           <t>B | 341呎 (1房)
 $1044万
 $30,625/呎
-(21年-05月-24日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -7716,7 +7716,7 @@
           <t>C | 212呎 (开放式)
 $691万
 $32,575/呎
-(24年-03月-17日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -7724,7 +7724,7 @@
           <t>D | 212呎 (开放式)
 $691万
 $32,575/呎
-(24年-03月-17日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -7732,7 +7732,7 @@
           <t>E | 344呎 (1房)
 $1050万
 $30,538/呎
-(21年-05月-01日)</t>
+(21年-05月)</t>
         </is>
       </c>
     </row>
@@ -7747,7 +7747,7 @@
           <t>A | 307呎 (1房)
 $1000万
 $32,567/呎
-(21年-10月-14日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -7755,7 +7755,7 @@
           <t>B | 341呎 (1房)
 $1017万
 $29,830/呎
-(21年-05月-23日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -7763,7 +7763,7 @@
           <t>C | 212呎 (开放式)
 $610万
 $28,750/呎
-(26年-01月-07日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -7771,7 +7771,7 @@
           <t>D | 212呎 (开放式)
 $687万
 $32,420/呎
-(24年-03月-17日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -7779,7 +7779,7 @@
           <t>E | 344呎 (1房)
 $987万
 $28,703/呎
-(21年-05月-24日)</t>
+(21年-05月)</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
           <t>A | 308呎 (1房)
 $929万
 $30,173/呎
-(25年-05月-28日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -7802,7 +7802,7 @@
           <t>B | 340呎 (1房)
 $992万
 $29,171/呎
-(20年-10月-21日)</t>
+(20年-10月)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -7810,7 +7810,7 @@
           <t>C | 212呎 (开放式)
 $684万
 $32,269/呎
-(22年-08月-01日)</t>
+(22年-08月)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -7818,7 +7818,7 @@
           <t>D | 212呎 (开放式)
 $684万
 $32,269/呎
-(24年-03月-17日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -7826,7 +7826,7 @@
           <t>E | 344呎 (1房)
 $964万
 $28,017/呎
-(21年-02月-25日)</t>
+(21年-02月)</t>
         </is>
       </c>
     </row>
@@ -7841,7 +7841,7 @@
           <t>A | 308呎 (1房)
 $982万
 $31,886/呎
-(21年-12月-22日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -7849,7 +7849,7 @@
           <t>B | 340呎 (1房)
 $1025万
 $30,156/呎
-(21年-03月-09日)</t>
+(21年-03月)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -7857,7 +7857,7 @@
           <t>C | 212呎 (开放式)
 $684万
 $32,259/呎
-(23年-10月-04日)</t>
+(23年-10月)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -7865,7 +7865,7 @@
           <t>D | 212呎 (开放式)
 $749万
 $35,330/呎
-(20年-06月-18日)</t>
+(20年-06月)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -7873,7 +7873,7 @@
           <t>E | 344呎 (1房)
 $962万
 $27,959/呎
-(21年-05月-23日)</t>
+(21年-05月)</t>
         </is>
       </c>
     </row>
@@ -7888,7 +7888,7 @@
           <t>A | 308呎 (1房)
 $920万
 $29,870/呎
-(25年-09月-21日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -7896,7 +7896,7 @@
           <t>B | 340呎 (1房)
 $978万
 $28,774/呎
-(21年-06月-06日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -7904,7 +7904,7 @@
           <t>C | 213呎 (开放式)
 $656万
 $30,808/呎
-(20年-06月-22日)</t>
+(20年-06月)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -7912,7 +7912,7 @@
           <t>D | 213呎 (开放式)
 $656万
 $30,808/呎
-(20年-02月-03日)</t>
+(20年-02月)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -7920,7 +7920,7 @@
           <t>E | 344呎 (1房)
 $996万
 $28,951/呎
-(20年-07月-19日)</t>
+(20年-07月)</t>
         </is>
       </c>
     </row>
@@ -7935,7 +7935,7 @@
           <t>A | 307呎 (1房)
 $947万
 $30,850/呎
-(21年-08月-08日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -7943,7 +7943,7 @@
           <t>B | 341呎 (1房)
 $965万
 $28,296/呎
-(21年-02月-17日)</t>
+(21年-02月)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -7951,7 +7951,7 @@
           <t>C | 213呎 (开放式)
 $702万
 $32,934/呎
-(20年-02月-03日)</t>
+(20年-02月)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -7959,7 +7959,7 @@
           <t>D | 212呎 (开放式)
 $702万
 $33,090/呎
-(20年-02月-04日)</t>
+(20年-02月)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -7967,7 +7967,7 @@
           <t>E | 344呎 (1房)
 $971万
 $28,230/呎
-(20年-07月-08日)</t>
+(20年-07月)</t>
         </is>
       </c>
     </row>
@@ -7982,7 +7982,7 @@
           <t>A | 307呎 (1房)
 $942万
 $30,697/呎
-(21年-09月-12日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -7990,7 +7990,7 @@
           <t>B | 340呎 (1房)
 $958万
 $28,182/呎
-(21年-05月-26日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -7998,7 +7998,7 @@
           <t>C | 212呎 (开放式)
 $636万
 $30,014/呎
-(20年-02月-05日)</t>
+(20年-02月)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -8006,7 +8006,7 @@
           <t>D | 213呎 (开放式)
 $667万
 $31,296/呎
-(20年-04月-15日)</t>
+(20年-04月)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -8014,7 +8014,7 @@
           <t>E | 344呎 (1房)
 $964万
 $28,035/呎
-(20年-06月-21日)</t>
+(20年-06月)</t>
         </is>
       </c>
     </row>
@@ -8029,7 +8029,7 @@
           <t>A | 308呎 (1房)
 $938万
 $30,445/呎
-(22年-07月-31日)</t>
+(22年-07月)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -8037,7 +8037,7 @@
           <t>B | 341呎 (1房)
 $997万
 $29,238/呎
-(20年-12月-30日)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -8045,7 +8045,7 @@
           <t>C | 212呎 (开放式)
 $692万
 $32,651/呎
-(20年-02月-03日)</t>
+(20年-02月)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -8053,7 +8053,7 @@
           <t>D | 212呎 (开放式)
 $692万
 $32,651/呎
-(20年-02月-03日)</t>
+(20年-02月)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -8061,7 +8061,7 @@
           <t>E | 344呎 (1房)
 $925万
 $26,881/呎
-(21年-05月-26日)</t>
+(21年-05月)</t>
         </is>
       </c>
     </row>
@@ -8076,7 +8076,7 @@
           <t>A | 308呎 (1房)
 $933万
 $30,292/呎
-(21年-12月-08日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -8084,7 +8084,7 @@
           <t>B | 341呎 (1房)
 $1000万
 $29,323/呎
-(21年-09月-29日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -8092,7 +8092,7 @@
           <t>C | 213呎 (开放式)
 $658万
 $30,878/呎
-(21年-06月-28日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -8100,7 +8100,7 @@
           <t>D | 212呎 (开放式)
 $628万
 $29,613/呎
-(20年-02月-04日)</t>
+(20年-02月)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -8108,7 +8108,7 @@
           <t>E | 344呎 (1房)
 $951万
 $27,648/呎
-(20年-05月-07日)</t>
+(20年-05月)</t>
         </is>
       </c>
     </row>
@@ -8123,7 +8123,7 @@
           <t>A | 308呎 (1房)
 $908万
 $29,464/呎
-(21年-07月-05日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -8131,7 +8131,7 @@
           <t>B | 340呎 (1房)
 $939万
 $27,609/呎
-(21年-04月-06日)</t>
+(21年-04月)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -8139,7 +8139,7 @@
           <t>C | 213呎 (开放式)
 $683万
 $32,070/呎
-(20年-02月-04日)</t>
+(20年-02月)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -8147,7 +8147,7 @@
           <t>D | 212呎 (开放式)
 $624万
 $29,420/呎
-(20年-02月-06日)</t>
+(20年-02月)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -8155,7 +8155,7 @@
           <t>E | 344呎 (1房)
 $999万
 $29,038/呎
-(20年-02月-05日)</t>
+(20年-02月)</t>
         </is>
       </c>
     </row>
@@ -8170,7 +8170,7 @@
           <t>A | 307呎 (1房)
 $885万
 $28,827/呎
-(21年-06月-02日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -8178,7 +8178,7 @@
           <t>B | 341呎 (1房)
 $1000万
 $29,323/呎
-(22年-04月-20日)</t>
+(22年-04月)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -8186,7 +8186,7 @@
           <t>C | 213呎 (开放式)
 $652万
 $30,610/呎
-(20年-01月-09日)</t>
+(20年-01月)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -8194,7 +8194,7 @@
           <t>D | 212呎 (开放式)
 $654万
 $30,844/呎
-(23年-08月-02日)</t>
+(23年-08月)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -8202,7 +8202,7 @@
           <t>E | 344呎 (1房)
 $910万
 $26,459/呎
-(20年-02月-06日)</t>
+(20年-02月)</t>
         </is>
       </c>
     </row>
@@ -8217,7 +8217,7 @@
           <t>A | 307呎 (1房)
 $870万
 $28,332/呎
-(21年-07月-08日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -8225,7 +8225,7 @@
           <t>B | 341呎 (1房)
 $926万
 $27,150/呎
-(21年-05月-25日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -8233,7 +8233,7 @@
           <t>C | 212呎 (开放式)
 $615万
 $29,024/呎
-(20年-02月-09日)</t>
+(20年-02月)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -8241,7 +8241,7 @@
           <t>D | 212呎 (开放式)
 $668万
 $31,509/呎
-(22年-05月-04日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -8249,7 +8249,7 @@
           <t>E | 344呎 (1房)
 $900万
 $26,148/呎
-(21年-03月-08日)</t>
+(21年-03月)</t>
         </is>
       </c>
     </row>
@@ -8264,7 +8264,7 @@
           <t>A | 308呎 (1房)
 $864万
 $28,045/呎
-(21年-08月-26日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -8272,7 +8272,7 @@
           <t>B | 340呎 (1房)
 $980万
 $28,824/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -8280,7 +8280,7 @@
           <t>C | 213呎 (开放式)
 $640万
 $30,061/呎
-(21年-08月-17日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -8288,7 +8288,7 @@
           <t>D | 212呎 (开放式)
 $633万
 $29,863/呎
-(20年-02月-04日)</t>
+(20年-02月)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -8296,7 +8296,7 @@
           <t>E | 344呎 (1房)
 $978万
 $28,445/呎
-(20年-04月-20日)</t>
+(20年-04月)</t>
         </is>
       </c>
     </row>
@@ -8311,7 +8311,7 @@
           <t>A | 307呎 (1房)
 $858万
 $27,945/呎
-(20年-06月-21日)</t>
+(20年-06月)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -8319,7 +8319,7 @@
           <t>B | 341呎 (1房)
 $913万
 $26,777/呎
-(21年-03月-23日)</t>
+(21年-03月)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -8327,7 +8327,7 @@
           <t>C | 212呎 (开放式)
 $636万
 $30,005/呎
-(21年-09月-01日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -8335,7 +8335,7 @@
           <t>D | 212呎 (开放式)
 $636万
 $30,005/呎
-(21年-06月-14日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -8343,7 +8343,7 @@
           <t>E | 344呎 (1房)
 $930万
 $27,020/呎
-(20年-05月-07日)</t>
+(20年-05月)</t>
         </is>
       </c>
     </row>
@@ -8358,7 +8358,7 @@
           <t>A | 307呎 (1房)
 $852万
 $27,752/呎
-(21年-11月-09日)</t>
+(21年-11月)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -8366,7 +8366,7 @@
           <t>B | 341呎 (1房)
 $907万
 $26,592/呎
-(21年-05月-26日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -8374,7 +8374,7 @@
           <t>C | 213呎 (开放式)
 $594万
 $27,883/呎
-(20年-05月-25日)</t>
+(20年-05月)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -8382,7 +8382,7 @@
           <t>D | 213呎 (开放式)
 $622万
 $29,211/呎
-(20年-10月-13日)</t>
+(20年-10月)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -8390,7 +8390,7 @@
           <t>E | 344呎 (1房)
 $873万
 $25,387/呎
-(20年-07月-14日)</t>
+(20年-07月)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-西营盘及上环-15 Western Street.xlsx
+++ b/files/港岛-西营盘及上环-15 Western Street.xlsx
@@ -7382,7 +7382,7 @@
           <t>A | 620呎 (3房)
 $2588万
 $41,748/呎
-(21年-07月)</t>
+(21年-07月-12日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -7390,7 +7390,7 @@
           <t>B | 564呎 (2房)
 $2272万
 $40,284/呎
-(21年-06月)</t>
+(21年-06月-28日)</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr"/>
@@ -7408,7 +7408,7 @@
           <t>A | 620呎 (3房)
 $2139万
 $34,502/呎
-(22年-02月)</t>
+(22年-02月-22日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -7416,7 +7416,7 @@
           <t>B | 530呎 (2房)
 $1807万
 $34,102/呎
-(22年-04月)</t>
+(22年-04月-18日)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr"/>
@@ -7434,7 +7434,7 @@
           <t>A | 620呎 (3房)
 $2045万
 $32,987/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -7442,7 +7442,7 @@
           <t>B | 530呎 (2房)
 $1722万
 $32,485/呎
-(21年-12月)</t>
+(21年-12月-12日)</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr"/>
@@ -7460,7 +7460,7 @@
           <t>A | 620呎 (3房)
 $1971万
 $31,787/呎
-(21年-04月)</t>
+(21年-04月-07日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -7468,7 +7468,7 @@
           <t>B | 530呎 (2房)
 $1714万
 $32,345/呎
-(21年-11月)</t>
+(21年-11月-30日)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr"/>
@@ -7486,7 +7486,7 @@
           <t>A | 661呎 (3房)
 $2414万
 $36,513/呎
-(21年-03月)</t>
+(21年-03月-09日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -7494,7 +7494,7 @@
           <t>B | 530呎 (2房)
 $1610万
 $30,375/呎
-(21年-04月)</t>
+(21年-04月-07日)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr"/>
@@ -7512,7 +7512,7 @@
           <t>A | 308呎 (1房)
 $1120万
 $36,364/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -7520,7 +7520,7 @@
           <t>B | 341呎 (1房)
 $1115万
 $32,695/呎
-(22年-04月)</t>
+(22年-04月-20日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -7528,7 +7528,7 @@
           <t>C | 212呎 (开放式)
 $756万
 $35,651/呎
-(24年-03月)</t>
+(24年-03月-26日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -7536,7 +7536,7 @@
           <t>D | 212呎 (开放式)
 $756万
 $35,651/呎
-(24年-03月)</t>
+(24年-03月-26日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -7544,7 +7544,7 @@
           <t>E | 344呎 (1房)
 $1141万
 $33,160/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
           <t>B | 341呎 (1房)
 $1097万
 $32,179/呎
-(21年-06月)</t>
+(21年-06月-24日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -7575,7 +7575,7 @@
           <t>C | 212呎 (开放式)
 $720万
 $33,953/呎
-(24年-03月)</t>
+(24年-03月-26日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -7583,7 +7583,7 @@
           <t>D | 212呎 (开放式)
 $720万
 $33,953/呎
-(24年-03月)</t>
+(24年-03月-26日)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -7591,7 +7591,7 @@
           <t>E | 344呎 (1房)
 $1097万
 $31,898/呎
-(21年-12月)</t>
+(21年-12月-09日)</t>
         </is>
       </c>
     </row>
@@ -7606,7 +7606,7 @@
           <t>A | 307呎 (1房)
 $1024万
 $33,355/呎
-(21年-12月)</t>
+(21年-12月-09日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -7614,7 +7614,7 @@
           <t>B | 341呎 (1房)
 $1065万
 $31,240/呎
-(21年-09月)</t>
+(21年-09月-23日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -7622,7 +7622,7 @@
           <t>C | 212呎 (开放式)
 $703万
 $33,156/呎
-(23年-12月)</t>
+(23年-12月-11日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -7630,7 +7630,7 @@
           <t>D | 212呎 (开放式)
 $698万
 $32,934/呎
-(24年-04月)</t>
+(24年-04月-10日)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -7638,7 +7638,7 @@
           <t>E | 344呎 (1房)
 $1065万
 $30,968/呎
-(21年-06月)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
     </row>
@@ -7653,7 +7653,7 @@
           <t>A | 307呎 (1房)
 $1016万
 $33,091/呎
-(21年-09月)</t>
+(21年-09月-09日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -7661,7 +7661,7 @@
           <t>B | 340呎 (1房)
 $1050万
 $30,871/呎
-(21年-08月)</t>
+(21年-08月-25日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -7669,7 +7669,7 @@
           <t>C | 212呎 (开放式)
 $699万
 $32,958/呎
-(24年-03月)</t>
+(24年-03月-17日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -7677,7 +7677,7 @@
           <t>D | 212呎 (开放式)
 $699万
 $32,958/呎
-(24年-03月)</t>
+(24年-03月-17日)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -7685,7 +7685,7 @@
           <t>E | 344呎 (1房)
 $1050万
 $30,512/呎
-(21年-11月)</t>
+(21年-11月-30日)</t>
         </is>
       </c>
     </row>
@@ -7700,7 +7700,7 @@
           <t>A | 308呎 (1房)
 $1008万
 $32,721/呎
-(22年-09月)</t>
+(22年-09月-26日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -7708,7 +7708,7 @@
           <t>B | 341呎 (1房)
 $1044万
 $30,625/呎
-(21年-05月)</t>
+(21年-05月-24日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -7716,7 +7716,7 @@
           <t>C | 212呎 (开放式)
 $691万
 $32,575/呎
-(24年-03月)</t>
+(24年-03月-17日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -7724,7 +7724,7 @@
           <t>D | 212呎 (开放式)
 $691万
 $32,575/呎
-(24年-03月)</t>
+(24年-03月-17日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -7732,7 +7732,7 @@
           <t>E | 344呎 (1房)
 $1050万
 $30,538/呎
-(21年-05月)</t>
+(21年-05月-01日)</t>
         </is>
       </c>
     </row>
@@ -7747,7 +7747,7 @@
           <t>A | 307呎 (1房)
 $1000万
 $32,567/呎
-(21年-10月)</t>
+(21年-10月-14日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -7755,7 +7755,7 @@
           <t>B | 341呎 (1房)
 $1017万
 $29,830/呎
-(21年-05月)</t>
+(21年-05月-23日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -7763,7 +7763,7 @@
           <t>C | 212呎 (开放式)
 $610万
 $28,750/呎
-(26年-01月)</t>
+(26年-01月-07日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -7771,7 +7771,7 @@
           <t>D | 212呎 (开放式)
 $687万
 $32,420/呎
-(24年-03月)</t>
+(24年-03月-17日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -7779,7 +7779,7 @@
           <t>E | 344呎 (1房)
 $987万
 $28,703/呎
-(21年-05月)</t>
+(21年-05月-24日)</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
           <t>A | 308呎 (1房)
 $929万
 $30,173/呎
-(25年-05月)</t>
+(25年-05月-28日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -7802,7 +7802,7 @@
           <t>B | 340呎 (1房)
 $992万
 $29,171/呎
-(20年-10月)</t>
+(20年-10月-21日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -7810,7 +7810,7 @@
           <t>C | 212呎 (开放式)
 $684万
 $32,269/呎
-(22年-08月)</t>
+(22年-08月-01日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -7818,7 +7818,7 @@
           <t>D | 212呎 (开放式)
 $684万
 $32,269/呎
-(24年-03月)</t>
+(24年-03月-17日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -7826,7 +7826,7 @@
           <t>E | 344呎 (1房)
 $964万
 $28,017/呎
-(21年-02月)</t>
+(21年-02月-25日)</t>
         </is>
       </c>
     </row>
@@ -7841,7 +7841,7 @@
           <t>A | 308呎 (1房)
 $982万
 $31,886/呎
-(21年-12月)</t>
+(21年-12月-22日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -7849,7 +7849,7 @@
           <t>B | 340呎 (1房)
 $1025万
 $30,156/呎
-(21年-03月)</t>
+(21年-03月-09日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -7857,7 +7857,7 @@
           <t>C | 212呎 (开放式)
 $684万
 $32,259/呎
-(23年-10月)</t>
+(23年-10月-04日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -7865,7 +7865,7 @@
           <t>D | 212呎 (开放式)
 $749万
 $35,330/呎
-(20年-06月)</t>
+(20年-06月-18日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -7873,7 +7873,7 @@
           <t>E | 344呎 (1房)
 $962万
 $27,959/呎
-(21年-05月)</t>
+(21年-05月-23日)</t>
         </is>
       </c>
     </row>
@@ -7888,7 +7888,7 @@
           <t>A | 308呎 (1房)
 $920万
 $29,870/呎
-(25年-09月)</t>
+(25年-09月-21日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -7896,7 +7896,7 @@
           <t>B | 340呎 (1房)
 $978万
 $28,774/呎
-(21年-06月)</t>
+(21年-06月-06日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -7904,7 +7904,7 @@
           <t>C | 213呎 (开放式)
 $656万
 $30,808/呎
-(20年-06月)</t>
+(20年-06月-22日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -7912,7 +7912,7 @@
           <t>D | 213呎 (开放式)
 $656万
 $30,808/呎
-(20年-02月)</t>
+(20年-02月-03日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -7920,7 +7920,7 @@
           <t>E | 344呎 (1房)
 $996万
 $28,951/呎
-(20年-07月)</t>
+(20年-07月-19日)</t>
         </is>
       </c>
     </row>
@@ -7935,7 +7935,7 @@
           <t>A | 307呎 (1房)
 $947万
 $30,850/呎
-(21年-08月)</t>
+(21年-08月-08日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -7943,7 +7943,7 @@
           <t>B | 341呎 (1房)
 $965万
 $28,296/呎
-(21年-02月)</t>
+(21年-02月-17日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -7951,7 +7951,7 @@
           <t>C | 213呎 (开放式)
 $702万
 $32,934/呎
-(20年-02月)</t>
+(20年-02月-03日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -7959,7 +7959,7 @@
           <t>D | 212呎 (开放式)
 $702万
 $33,090/呎
-(20年-02月)</t>
+(20年-02月-04日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -7967,7 +7967,7 @@
           <t>E | 344呎 (1房)
 $971万
 $28,230/呎
-(20年-07月)</t>
+(20年-07月-08日)</t>
         </is>
       </c>
     </row>
@@ -7982,7 +7982,7 @@
           <t>A | 307呎 (1房)
 $942万
 $30,697/呎
-(21年-09月)</t>
+(21年-09月-12日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -7990,7 +7990,7 @@
           <t>B | 340呎 (1房)
 $958万
 $28,182/呎
-(21年-05月)</t>
+(21年-05月-26日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -7998,7 +7998,7 @@
           <t>C | 212呎 (开放式)
 $636万
 $30,014/呎
-(20年-02月)</t>
+(20年-02月-05日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -8006,7 +8006,7 @@
           <t>D | 213呎 (开放式)
 $667万
 $31,296/呎
-(20年-04月)</t>
+(20年-04月-15日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -8014,7 +8014,7 @@
           <t>E | 344呎 (1房)
 $964万
 $28,035/呎
-(20年-06月)</t>
+(20年-06月-21日)</t>
         </is>
       </c>
     </row>
@@ -8029,7 +8029,7 @@
           <t>A | 308呎 (1房)
 $938万
 $30,445/呎
-(22年-07月)</t>
+(22年-07月-31日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -8037,7 +8037,7 @@
           <t>B | 341呎 (1房)
 $997万
 $29,238/呎
-(20年-12月)</t>
+(20年-12月-30日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -8045,7 +8045,7 @@
           <t>C | 212呎 (开放式)
 $692万
 $32,651/呎
-(20年-02月)</t>
+(20年-02月-03日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -8053,7 +8053,7 @@
           <t>D | 212呎 (开放式)
 $692万
 $32,651/呎
-(20年-02月)</t>
+(20年-02月-03日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -8061,7 +8061,7 @@
           <t>E | 344呎 (1房)
 $925万
 $26,881/呎
-(21年-05月)</t>
+(21年-05月-26日)</t>
         </is>
       </c>
     </row>
@@ -8076,7 +8076,7 @@
           <t>A | 308呎 (1房)
 $933万
 $30,292/呎
-(21年-12月)</t>
+(21年-12月-08日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -8084,7 +8084,7 @@
           <t>B | 341呎 (1房)
 $1000万
 $29,323/呎
-(21年-09月)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -8092,7 +8092,7 @@
           <t>C | 213呎 (开放式)
 $658万
 $30,878/呎
-(21年-06月)</t>
+(21年-06月-28日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -8100,7 +8100,7 @@
           <t>D | 212呎 (开放式)
 $628万
 $29,613/呎
-(20年-02月)</t>
+(20年-02月-04日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -8108,7 +8108,7 @@
           <t>E | 344呎 (1房)
 $951万
 $27,648/呎
-(20年-05月)</t>
+(20年-05月-07日)</t>
         </is>
       </c>
     </row>
@@ -8123,7 +8123,7 @@
           <t>A | 308呎 (1房)
 $908万
 $29,464/呎
-(21年-07月)</t>
+(21年-07月-05日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -8131,7 +8131,7 @@
           <t>B | 340呎 (1房)
 $939万
 $27,609/呎
-(21年-04月)</t>
+(21年-04月-06日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -8139,7 +8139,7 @@
           <t>C | 213呎 (开放式)
 $683万
 $32,070/呎
-(20年-02月)</t>
+(20年-02月-04日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -8147,7 +8147,7 @@
           <t>D | 212呎 (开放式)
 $624万
 $29,420/呎
-(20年-02月)</t>
+(20年-02月-06日)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -8155,7 +8155,7 @@
           <t>E | 344呎 (1房)
 $999万
 $29,038/呎
-(20年-02月)</t>
+(20年-02月-05日)</t>
         </is>
       </c>
     </row>
@@ -8170,7 +8170,7 @@
           <t>A | 307呎 (1房)
 $885万
 $28,827/呎
-(21年-06月)</t>
+(21年-06月-02日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -8178,7 +8178,7 @@
           <t>B | 341呎 (1房)
 $1000万
 $29,323/呎
-(22年-04月)</t>
+(22年-04月-20日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -8186,7 +8186,7 @@
           <t>C | 213呎 (开放式)
 $652万
 $30,610/呎
-(20年-01月)</t>
+(20年-01月-09日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -8194,7 +8194,7 @@
           <t>D | 212呎 (开放式)
 $654万
 $30,844/呎
-(23年-08月)</t>
+(23年-08月-02日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -8202,7 +8202,7 @@
           <t>E | 344呎 (1房)
 $910万
 $26,459/呎
-(20年-02月)</t>
+(20年-02月-06日)</t>
         </is>
       </c>
     </row>
@@ -8217,7 +8217,7 @@
           <t>A | 307呎 (1房)
 $870万
 $28,332/呎
-(21年-07月)</t>
+(21年-07月-08日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -8225,7 +8225,7 @@
           <t>B | 341呎 (1房)
 $926万
 $27,150/呎
-(21年-05月)</t>
+(21年-05月-25日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -8233,7 +8233,7 @@
           <t>C | 212呎 (开放式)
 $615万
 $29,024/呎
-(20年-02月)</t>
+(20年-02月-09日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -8241,7 +8241,7 @@
           <t>D | 212呎 (开放式)
 $668万
 $31,509/呎
-(22年-05月)</t>
+(22年-05月-04日)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -8249,7 +8249,7 @@
           <t>E | 344呎 (1房)
 $900万
 $26,148/呎
-(21年-03月)</t>
+(21年-03月-08日)</t>
         </is>
       </c>
     </row>
@@ -8264,7 +8264,7 @@
           <t>A | 308呎 (1房)
 $864万
 $28,045/呎
-(21年-08月)</t>
+(21年-08月-26日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -8272,7 +8272,7 @@
           <t>B | 340呎 (1房)
 $980万
 $28,824/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -8280,7 +8280,7 @@
           <t>C | 213呎 (开放式)
 $640万
 $30,061/呎
-(21年-08月)</t>
+(21年-08月-17日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -8288,7 +8288,7 @@
           <t>D | 212呎 (开放式)
 $633万
 $29,863/呎
-(20年-02月)</t>
+(20年-02月-04日)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -8296,7 +8296,7 @@
           <t>E | 344呎 (1房)
 $978万
 $28,445/呎
-(20年-04月)</t>
+(20年-04月-20日)</t>
         </is>
       </c>
     </row>
@@ -8311,7 +8311,7 @@
           <t>A | 307呎 (1房)
 $858万
 $27,945/呎
-(20年-06月)</t>
+(20年-06月-21日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -8319,7 +8319,7 @@
           <t>B | 341呎 (1房)
 $913万
 $26,777/呎
-(21年-03月)</t>
+(21年-03月-23日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -8327,7 +8327,7 @@
           <t>C | 212呎 (开放式)
 $636万
 $30,005/呎
-(21年-09月)</t>
+(21年-09月-01日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -8335,7 +8335,7 @@
           <t>D | 212呎 (开放式)
 $636万
 $30,005/呎
-(21年-06月)</t>
+(21年-06月-14日)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -8343,7 +8343,7 @@
           <t>E | 344呎 (1房)
 $930万
 $27,020/呎
-(20年-05月)</t>
+(20年-05月-07日)</t>
         </is>
       </c>
     </row>
@@ -8358,7 +8358,7 @@
           <t>A | 307呎 (1房)
 $852万
 $27,752/呎
-(21年-11月)</t>
+(21年-11月-09日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -8366,7 +8366,7 @@
           <t>B | 341呎 (1房)
 $907万
 $26,592/呎
-(21年-05月)</t>
+(21年-05月-26日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -8374,7 +8374,7 @@
           <t>C | 213呎 (开放式)
 $594万
 $27,883/呎
-(20年-05月)</t>
+(20年-05月-25日)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -8382,7 +8382,7 @@
           <t>D | 213呎 (开放式)
 $622万
 $29,211/呎
-(20年-10月)</t>
+(20年-10月-13日)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -8390,7 +8390,7 @@
           <t>E | 344呎 (1房)
 $873万
 $25,387/呎
-(20年-07月)</t>
+(20年-07月-14日)</t>
         </is>
       </c>
     </row>
